--- a/core/public/file/MaufileDsPhong.xlsx
+++ b/core/public/file/MaufileDsPhong.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qlks\core\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>Tên phòng</t>
   </si>
@@ -40,25 +40,46 @@
     <t>Trạng thái</t>
   </si>
   <si>
-    <t>Phòng 1</t>
-  </si>
-  <si>
-    <t>HP0001</t>
-  </si>
-  <si>
-    <t>Phòng 2</t>
-  </si>
-  <si>
-    <t>HP0002</t>
-  </si>
-  <si>
     <t>Mô tả</t>
   </si>
   <si>
-    <t>Mã Loại phòng</t>
-  </si>
-  <si>
     <t>Mã phòng</t>
+  </si>
+  <si>
+    <t>Mã loại phòng</t>
+  </si>
+  <si>
+    <t>Phòng 02</t>
+  </si>
+  <si>
+    <t>Phòng 01</t>
+  </si>
+  <si>
+    <t>Hướng phòng</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Số người</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Số giường</t>
+  </si>
+  <si>
+    <t>HP0015</t>
+  </si>
+  <si>
+    <t>ML01</t>
+  </si>
+  <si>
+    <t>ML02</t>
   </si>
 </sst>
 </file>
@@ -115,7 +136,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left"/>
@@ -146,14 +179,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tableTable" displayName="tableTable" ref="A1:E20" totalsRowShown="0">
-  <autoFilter ref="A1:E20"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Tên phòng" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tableTable" displayName="tableTable" ref="A1:H20" totalsRowShown="0">
+  <autoFilter ref="A1:H20"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Mã loại phòng" dataDxfId="6"/>
     <tableColumn id="7" name="Mã phòng"/>
-    <tableColumn id="2" name="Mã Loại phòng" dataDxfId="2"/>
-    <tableColumn id="5" name="Trạng thái" dataDxfId="1"/>
-    <tableColumn id="6" name="Mô tả" dataDxfId="0"/>
+    <tableColumn id="2" name="Tên phòng" dataDxfId="5"/>
+    <tableColumn id="4" name="Số giường" dataDxfId="1"/>
+    <tableColumn id="5" name="Số người" dataDxfId="4"/>
+    <tableColumn id="8" name="Hướng phòng" dataDxfId="0"/>
+    <tableColumn id="6" name="Trạng thái" dataDxfId="3"/>
+    <tableColumn id="3" name="Mô tả" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -446,176 +482,255 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" customWidth="1"/>
+    <col min="2" max="4" width="21" customWidth="1"/>
+    <col min="5" max="6" width="35.5703125" customWidth="1"/>
+    <col min="7" max="7" width="29.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/core/public/file/MaufileDsPhong.xlsx
+++ b/core/public/file/MaufileDsPhong.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -43,18 +43,9 @@
     <t>Mô tả</t>
   </si>
   <si>
-    <t>Mã phòng</t>
-  </si>
-  <si>
     <t>Mã loại phòng</t>
   </si>
   <si>
-    <t>Phòng 02</t>
-  </si>
-  <si>
-    <t>Phòng 01</t>
-  </si>
-  <si>
     <t>Hướng phòng</t>
   </si>
   <si>
@@ -80,6 +71,15 @@
   </si>
   <si>
     <t>ML02</t>
+  </si>
+  <si>
+    <t>Mã  phòng</t>
+  </si>
+  <si>
+    <t>Phòng 01 test</t>
+  </si>
+  <si>
+    <t>Phòng 02 test</t>
   </si>
 </sst>
 </file>
@@ -139,7 +139,11 @@
   <dxfs count="7">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -151,11 +155,7 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -183,13 +183,13 @@
   <autoFilter ref="A1:H20"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Mã loại phòng" dataDxfId="6"/>
-    <tableColumn id="7" name="Mã phòng"/>
+    <tableColumn id="7" name="Mã  phòng"/>
     <tableColumn id="2" name="Tên phòng" dataDxfId="5"/>
-    <tableColumn id="4" name="Số giường" dataDxfId="1"/>
-    <tableColumn id="5" name="Số người" dataDxfId="4"/>
-    <tableColumn id="8" name="Hướng phòng" dataDxfId="0"/>
-    <tableColumn id="6" name="Trạng thái" dataDxfId="3"/>
-    <tableColumn id="3" name="Mô tả" dataDxfId="2"/>
+    <tableColumn id="4" name="Số giường" dataDxfId="4"/>
+    <tableColumn id="5" name="Số người" dataDxfId="3"/>
+    <tableColumn id="8" name="Hướng phòng" dataDxfId="2"/>
+    <tableColumn id="6" name="Trạng thái" dataDxfId="1"/>
+    <tableColumn id="3" name="Mô tả" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -494,22 +494,22 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>1</v>
@@ -520,45 +520,45 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H3" s="3"/>
     </row>
